--- a/IA, 메뉴구조도/FO/(아이뱅크) TOPIK_Myanmar_FO_IA, 메뉴구조도_v1.1.xlsx
+++ b/IA, 메뉴구조도/FO/(아이뱅크) TOPIK_Myanmar_FO_IA, 메뉴구조도_v1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhcho/Documents/Myanmar/IA, 메뉴구조도/FO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E2760C-01A2-7844-8F92-D83BE78686A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5D10D4-470A-D648-8367-8A9C13F69402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1063,7 +1063,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>한글/영문 성명 · 생년월일 · 성별 · 국적 · 제1언어 · 연락처 · 직업 · 응시동기 · 응시목적 · 여권번호 · 증명사진 업로드(jpg,png/3:4 비율/200KB~2MB) + 인라인 에러</t>
+    <t>한글/영문 성명 · 생년월일 · 성별 · 국적 · 제1언어 · 연락처 · 직업 · 응시동기 · 응시목적 · 증명사진 업로드(jpg,png/3:4 비율/200KB~2MB) + 인라인 에러</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
